--- a/test.xlsx
+++ b/test.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\izrantsevavs\Documents\portfolio\my\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E00CAE0-6479-43E8-9BB1-C62BEE8BB9E4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2085DA3-9239-4017-8444-CE24C47FA44D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="83">
   <si>
     <t>Тигр</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>Команда</t>
+  </si>
+  <si>
+    <t>Кумите</t>
   </si>
 </sst>
 </file>
@@ -320,7 +323,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -335,6 +338,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -615,14 +620,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="13" customWidth="1"/>
-    <col min="11" max="12" width="9.140625" style="5"/>
+    <col min="11" max="13" width="9.140625" style="5"/>
+    <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -659,8 +665,11 @@
       <c r="L1" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -671,7 +680,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="3">
-        <v>42144</v>
+        <v>42875</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>8</v>
@@ -697,8 +706,19 @@
       <c r="L2" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M2" s="5">
+        <v>1</v>
+      </c>
+      <c r="N2" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46266</v>
+      </c>
+      <c r="O2" s="7">
+        <f ca="1">($N$2-D2)/365.25</f>
+        <v>9.2840520191649549</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -709,7 +729,7 @@
         <v>23</v>
       </c>
       <c r="D3" s="3">
-        <v>42145</v>
+        <v>42876</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>8</v>
@@ -735,8 +755,15 @@
       <c r="L3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="O3" s="7">
+        <f t="shared" ref="O3:O16" ca="1" si="0">($N$2-D3)/365.25</f>
+        <v>9.2813141683778237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
@@ -747,7 +774,7 @@
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>42146</v>
+        <v>42877</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>8</v>
@@ -770,8 +797,15 @@
       <c r="L4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M4" s="5">
+        <v>1</v>
+      </c>
+      <c r="O4" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.2785763175906908</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
@@ -782,7 +816,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="3">
-        <v>42147</v>
+        <v>42878</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>8</v>
@@ -802,8 +836,15 @@
       <c r="K5" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="O5" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.2758384668035596</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -814,7 +855,7 @@
         <v>29</v>
       </c>
       <c r="D6" s="3">
-        <v>42148</v>
+        <v>42879</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>8</v>
@@ -834,8 +875,15 @@
       <c r="K6" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M6" s="5">
+        <v>1</v>
+      </c>
+      <c r="O6" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.2731006160164267</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>21</v>
       </c>
@@ -846,7 +894,7 @@
         <v>31</v>
       </c>
       <c r="D7" s="3">
-        <v>42149</v>
+        <v>42880</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>8</v>
@@ -863,8 +911,15 @@
       <c r="I7" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M7" s="5">
+        <v>1</v>
+      </c>
+      <c r="O7" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.2703627652292955</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>42</v>
       </c>
@@ -875,7 +930,7 @@
         <v>44</v>
       </c>
       <c r="D8" s="3">
-        <v>42150</v>
+        <v>42881</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>8</v>
@@ -901,8 +956,12 @@
       <c r="L8" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O8" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.2676249144421625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>46</v>
       </c>
@@ -913,7 +972,7 @@
         <v>48</v>
       </c>
       <c r="D9" s="3">
-        <v>42151</v>
+        <v>42882</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>8</v>
@@ -936,8 +995,12 @@
       <c r="L9" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O9" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.2648870636550313</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>50</v>
       </c>
@@ -948,7 +1011,7 @@
         <v>52</v>
       </c>
       <c r="D10" s="3">
-        <v>42152</v>
+        <v>42883</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>8</v>
@@ -971,8 +1034,12 @@
       <c r="L10" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O10" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.2621492128678984</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>54</v>
       </c>
@@ -983,7 +1050,7 @@
         <v>56</v>
       </c>
       <c r="D11" s="3">
-        <v>42153</v>
+        <v>42884</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>8</v>
@@ -1000,8 +1067,12 @@
       <c r="I11" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O11" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.2594113620807672</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>59</v>
       </c>
@@ -1012,7 +1083,7 @@
         <v>61</v>
       </c>
       <c r="D12" s="3">
-        <v>42154</v>
+        <v>42885</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>8</v>
@@ -1029,8 +1100,12 @@
       <c r="I12" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O12" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.2566735112936342</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>63</v>
       </c>
@@ -1041,7 +1116,7 @@
         <v>65</v>
       </c>
       <c r="D13" s="3">
-        <v>42155</v>
+        <v>42886</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>8</v>
@@ -1058,8 +1133,12 @@
       <c r="I13" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O13" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.2539356605065031</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>67</v>
       </c>
@@ -1070,7 +1149,7 @@
         <v>69</v>
       </c>
       <c r="D14" s="3">
-        <v>42156</v>
+        <v>42887</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>8</v>
@@ -1093,8 +1172,12 @@
       <c r="L14" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O14" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.2511978097193701</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>71</v>
       </c>
@@ -1105,7 +1188,7 @@
         <v>73</v>
       </c>
       <c r="D15" s="3">
-        <v>42157</v>
+        <v>42888</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>8</v>
@@ -1128,8 +1211,12 @@
       <c r="L15" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O15" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.2484599589322389</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>75</v>
       </c>
@@ -1140,7 +1227,7 @@
         <v>77</v>
       </c>
       <c r="D16" s="3">
-        <v>42158</v>
+        <v>42889</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>8</v>
@@ -1162,6 +1249,10 @@
       </c>
       <c r="L16" s="5">
         <v>1</v>
+      </c>
+      <c r="O16" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.245722108145106</v>
       </c>
     </row>
   </sheetData>
